--- a/scripts/data/50m_Masculino_Absoluto_Espalda.xlsx
+++ b/scripts/data/50m_Masculino_Absoluto_Espalda.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1520,13 +1520,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F26" t="str">
-        <v>00:00:37.69</v>
+        <v>00:00:37.01</v>
       </c>
       <c r="G26">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="H26" s="1">
-        <v>46082.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I26" t="str">
         <v>Deportista</v>
@@ -1538,10 +1538,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L26" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M26" t="str">
-        <v>CASTELLÓN</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N26" t="str">
         <v>No</v>
@@ -2479,22 +2479,22 @@
         <v>100 Espalda</v>
       </c>
       <c r="C48" t="str">
-        <v>GONZALO YUSTE TRUJILLO</v>
+        <v>MARCOS PEDRERO MARTINEZ</v>
       </c>
       <c r="D48">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="E48" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F48" t="str">
-        <v>00:01:24.50</v>
+        <v>00:01:20.98</v>
       </c>
       <c r="G48">
-        <v>228</v>
+        <v>259</v>
       </c>
       <c r="H48" s="1">
-        <v>45683.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I48" t="str">
         <v>Deportista</v>
@@ -2506,13 +2506,13 @@
         <v>Electrónico</v>
       </c>
       <c r="L48" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M48" t="str">
-        <v>Elche</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N48" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="49">
@@ -2523,7 +2523,7 @@
         <v>100 Espalda</v>
       </c>
       <c r="C49" t="str">
-        <v>JUAN CAMACHO MARTINEZ</v>
+        <v>GONZALO YUSTE TRUJILLO</v>
       </c>
       <c r="D49">
         <v>2010</v>
@@ -2532,13 +2532,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F49" t="str">
-        <v>00:02:34.44</v>
+        <v>00:01:24.50</v>
       </c>
       <c r="G49">
-        <v>37</v>
+        <v>228</v>
       </c>
       <c r="H49" s="1">
-        <v>46172.99949074074</v>
+        <v>45683.99949074074</v>
       </c>
       <c r="I49" t="str">
         <v>Deportista</v>
@@ -2547,13 +2547,13 @@
         <v>50m</v>
       </c>
       <c r="K49" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L49" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M49" t="str">
-        <v>Vila-Real</v>
+        <v>Elche</v>
       </c>
       <c r="N49" t="str">
         <v>Sí</v>
@@ -2561,13 +2561,13 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B50" t="str">
-        <v>200 Espalda</v>
+        <v>100 Espalda</v>
       </c>
       <c r="C50" t="str">
-        <v>CARLOS MENDEZ SALVADOR</v>
+        <v>JUAN CAMACHO MARTINEZ</v>
       </c>
       <c r="D50">
         <v>2010</v>
@@ -2576,13 +2576,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F50" t="str">
-        <v>00:02:18.80</v>
+        <v>00:02:34.44</v>
       </c>
       <c r="G50">
-        <v>524</v>
+        <v>37</v>
       </c>
       <c r="H50" s="1">
-        <v>46144.99949074074</v>
+        <v>46172.99949074074</v>
       </c>
       <c r="I50" t="str">
         <v>Deportista</v>
@@ -2591,42 +2591,42 @@
         <v>50m</v>
       </c>
       <c r="K50" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L50" t="str">
-        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M50" t="str">
-        <v>ZARAGOZA (C)</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N50" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B51" t="str">
         <v>200 Espalda</v>
       </c>
       <c r="C51" t="str">
-        <v>ALVARO TERUEL BELLOCH</v>
+        <v>CARLOS MENDEZ SALVADOR</v>
       </c>
       <c r="D51">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="E51" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F51" t="str">
-        <v>00:02:22.42</v>
+        <v>00:02:18.80</v>
       </c>
       <c r="G51">
-        <v>485</v>
+        <v>524</v>
       </c>
       <c r="H51" s="1">
-        <v>46074.99949074074</v>
+        <v>46144.99949074074</v>
       </c>
       <c r="I51" t="str">
         <v>Deportista</v>
@@ -2638,10 +2638,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L51" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2026</v>
+        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
       </c>
       <c r="M51" t="str">
-        <v>Elche</v>
+        <v>ZARAGOZA (C)</v>
       </c>
       <c r="N51" t="str">
         <v>No</v>
@@ -2649,28 +2649,28 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B52" t="str">
         <v>200 Espalda</v>
       </c>
       <c r="C52" t="str">
-        <v>MARCOS ESCOBEDO IRURETA</v>
+        <v>ALVARO TERUEL BELLOCH</v>
       </c>
       <c r="D52">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="E52" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F52" t="str">
-        <v>00:02:25.44</v>
+        <v>00:02:22.42</v>
       </c>
       <c r="G52">
-        <v>456</v>
+        <v>485</v>
       </c>
       <c r="H52" s="1">
-        <v>45494.99949074074</v>
+        <v>46074.99949074074</v>
       </c>
       <c r="I52" t="str">
         <v>Deportista</v>
@@ -2682,10 +2682,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L52" t="str">
-        <v>Campeonato Autonómico Open Junior Y Absoluto de Verano</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2026</v>
       </c>
       <c r="M52" t="str">
-        <v>Castellón</v>
+        <v>Elche</v>
       </c>
       <c r="N52" t="str">
         <v>No</v>
@@ -2693,28 +2693,28 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B53" t="str">
         <v>200 Espalda</v>
       </c>
       <c r="C53" t="str">
-        <v>MARTIN FABIA NOGUERA</v>
+        <v>MARCOS ESCOBEDO IRURETA</v>
       </c>
       <c r="D53">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="E53" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F53" t="str">
-        <v>00:02:32.27</v>
+        <v>00:02:25.44</v>
       </c>
       <c r="G53">
-        <v>397</v>
+        <v>456</v>
       </c>
       <c r="H53" s="1">
-        <v>44576.99949074074</v>
+        <v>45494.99949074074</v>
       </c>
       <c r="I53" t="str">
         <v>Deportista</v>
@@ -2726,10 +2726,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L53" t="str">
-        <v>Autonomico Infantil de Invierno</v>
+        <v>Campeonato Autonómico Open Junior Y Absoluto de Verano</v>
       </c>
       <c r="M53" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N53" t="str">
         <v>No</v>
@@ -2737,28 +2737,28 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B54" t="str">
         <v>200 Espalda</v>
       </c>
       <c r="C54" t="str">
-        <v>ALEXIS GARCIA VALERO</v>
+        <v>MARTIN FABIA NOGUERA</v>
       </c>
       <c r="D54">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="E54" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F54" t="str">
-        <v>00:02:37.79</v>
+        <v>00:02:32.27</v>
       </c>
       <c r="G54">
-        <v>357</v>
+        <v>397</v>
       </c>
       <c r="H54" s="1">
-        <v>46081.99949074074</v>
+        <v>44576.99949074074</v>
       </c>
       <c r="I54" t="str">
         <v>Deportista</v>
@@ -2770,10 +2770,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L54" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>Autonomico Infantil de Invierno</v>
       </c>
       <c r="M54" t="str">
-        <v>CASTELLÓN</v>
+        <v>Elche</v>
       </c>
       <c r="N54" t="str">
         <v>No</v>
@@ -2781,13 +2781,13 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B55" t="str">
         <v>200 Espalda</v>
       </c>
       <c r="C55" t="str">
-        <v>NEIZAN DE LUCA RUBIO</v>
+        <v>ALEXIS GARCIA VALERO</v>
       </c>
       <c r="D55">
         <v>2011</v>
@@ -2796,13 +2796,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F55" t="str">
-        <v>00:02:38.06</v>
+        <v>00:02:37.63</v>
       </c>
       <c r="G55">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="H55" s="1">
-        <v>46047.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I55" t="str">
         <v>Deportista</v>
@@ -2814,10 +2814,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L55" t="str">
-        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M55" t="str">
-        <v>Elche</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N55" t="str">
         <v>No</v>
@@ -2825,28 +2825,28 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B56" t="str">
         <v>200 Espalda</v>
       </c>
       <c r="C56" t="str">
-        <v>ADRIAN CRUZ MARTIN</v>
+        <v>NEIZAN DE LUCA RUBIO</v>
       </c>
       <c r="D56">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="E56" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F56" t="str">
-        <v>00:02:41.23</v>
+        <v>00:02:38.06</v>
       </c>
       <c r="G56">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="H56" s="1">
-        <v>45683.99949074074</v>
+        <v>46047.99949074074</v>
       </c>
       <c r="I56" t="str">
         <v>Deportista</v>
@@ -2858,7 +2858,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L56" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M56" t="str">
         <v>Elche</v>
@@ -2869,28 +2869,28 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B57" t="str">
         <v>200 Espalda</v>
       </c>
       <c r="C57" t="str">
-        <v>HECTOR ALFARO OROZCO</v>
+        <v>ADRIAN CRUZ MARTIN</v>
       </c>
       <c r="D57">
-        <v>2005</v>
+        <v>2009</v>
       </c>
       <c r="E57" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F57" t="str">
-        <v>00:02:42.18</v>
+        <v>00:02:41.23</v>
       </c>
       <c r="G57">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="H57" s="1">
-        <v>44709.99949074074</v>
+        <v>45683.99949074074</v>
       </c>
       <c r="I57" t="str">
         <v>Deportista</v>
@@ -2899,13 +2899,13 @@
         <v>50m</v>
       </c>
       <c r="K57" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L57" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M57" t="str">
-        <v>Sedavi</v>
+        <v>Elche</v>
       </c>
       <c r="N57" t="str">
         <v>No</v>
@@ -2913,28 +2913,28 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B58" t="str">
         <v>200 Espalda</v>
       </c>
       <c r="C58" t="str">
-        <v>IKER BARTOLIN GIMENEZ</v>
+        <v>HECTOR ALFARO OROZCO</v>
       </c>
       <c r="D58">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="E58" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F58" t="str">
-        <v>00:02:43.21</v>
+        <v>00:02:42.18</v>
       </c>
       <c r="G58">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="H58" s="1">
-        <v>45710.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I58" t="str">
         <v>Deportista</v>
@@ -2943,13 +2943,13 @@
         <v>50m</v>
       </c>
       <c r="K58" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L58" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M58" t="str">
-        <v>ELCHE</v>
+        <v>Sedavi</v>
       </c>
       <c r="N58" t="str">
         <v>No</v>
@@ -2957,28 +2957,28 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B59" t="str">
         <v>200 Espalda</v>
       </c>
       <c r="C59" t="str">
-        <v>GERMAN MALLO FAURE</v>
+        <v>IKER BARTOLIN GIMENEZ</v>
       </c>
       <c r="D59">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="E59" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F59" t="str">
-        <v>00:02:53.26</v>
+        <v>00:02:43.21</v>
       </c>
       <c r="G59">
-        <v>270</v>
+        <v>322</v>
       </c>
       <c r="H59" s="1">
-        <v>44976.99949074074</v>
+        <v>45710.99949074074</v>
       </c>
       <c r="I59" t="str">
         <v>Deportista</v>
@@ -2990,10 +2990,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L59" t="str">
-        <v>Trofeo Internacional XXVIII Memorial Pascual Roman</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
       </c>
       <c r="M59" t="str">
-        <v>Elche</v>
+        <v>ELCHE</v>
       </c>
       <c r="N59" t="str">
         <v>No</v>
@@ -3001,28 +3001,28 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B60" t="str">
         <v>200 Espalda</v>
       </c>
       <c r="C60" t="str">
-        <v>GONZALO YUSTE TRUJILLO</v>
+        <v>GERMAN MALLO FAURE</v>
       </c>
       <c r="D60">
-        <v>2010</v>
+        <v>2004</v>
       </c>
       <c r="E60" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F60" t="str">
-        <v>00:02:58.73</v>
+        <v>00:02:53.26</v>
       </c>
       <c r="G60">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="H60" s="1">
-        <v>45683.99949074074</v>
+        <v>44976.99949074074</v>
       </c>
       <c r="I60" t="str">
         <v>Deportista</v>
@@ -3034,7 +3034,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L60" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>Trofeo Internacional XXVIII Memorial Pascual Roman</v>
       </c>
       <c r="M60" t="str">
         <v>Elche</v>
@@ -3043,9 +3043,53 @@
         <v>No</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61">
+        <v>11</v>
+      </c>
+      <c r="B61" t="str">
+        <v>200 Espalda</v>
+      </c>
+      <c r="C61" t="str">
+        <v>GONZALO YUSTE TRUJILLO</v>
+      </c>
+      <c r="D61">
+        <v>2010</v>
+      </c>
+      <c r="E61" t="str">
+        <v>C.N. MEDITERRANEO VALENCIA</v>
+      </c>
+      <c r="F61" t="str">
+        <v>00:02:58.73</v>
+      </c>
+      <c r="G61">
+        <v>246</v>
+      </c>
+      <c r="H61" s="1">
+        <v>45683.99949074074</v>
+      </c>
+      <c r="I61" t="str">
+        <v>Deportista</v>
+      </c>
+      <c r="J61" t="str">
+        <v>50m</v>
+      </c>
+      <c r="K61" t="str">
+        <v>Electrónico</v>
+      </c>
+      <c r="L61" t="str">
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+      </c>
+      <c r="M61" t="str">
+        <v>Elche</v>
+      </c>
+      <c r="N61" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O61"/>
   </ignoredErrors>
 </worksheet>
 </file>